--- a/data/dividends_info_20260319.xlsx
+++ b/data/dividends_info_20260319.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>51.45000076293945</v>
+        <v>51.29999923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>1.360544197511898</v>
+        <v>1.364522437447329</v>
       </c>
       <c r="J2" t="n">
         <v>340</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5.659999847412109</v>
+        <v>5.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3.533568999855095</v>
+        <v>3.636363636363637</v>
       </c>
       <c r="J3" t="n">
         <v>242</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>18.5</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I4" t="n">
-        <v>2.032432432432433</v>
+        <v>2.000000081163775</v>
       </c>
       <c r="J4" t="n">
         <v>123</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.140000104904175</v>
+        <v>2.119999885559082</v>
       </c>
       <c r="I5" t="n">
-        <v>3.971962422114281</v>
+        <v>4.009434178699683</v>
       </c>
       <c r="J5" t="n">
         <v>109</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>31.29999923706055</v>
+        <v>31.54999923706055</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4792332385184008</v>
+        <v>0.475435827661767</v>
       </c>
       <c r="J6" t="n">
         <v>109</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>22</v>
+        <v>22.02000045776367</v>
       </c>
       <c r="I7" t="n">
-        <v>1.136363636363636</v>
+        <v>1.135331493201021</v>
       </c>
       <c r="J7" t="n">
         <v>95</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.14999961853027</v>
+        <v>20.10000038146973</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9219858322321364</v>
+        <v>0.9701492353192755</v>
       </c>
       <c r="J8" t="n">
         <v>95</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>64.26000213623047</v>
+        <v>63.20000076293945</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9803921242710314</v>
+        <v>0.99683543100435</v>
       </c>
       <c r="J9" t="n">
         <v>95</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>21.72999954223633</v>
+        <v>21.46999931335449</v>
       </c>
       <c r="I10" t="n">
-        <v>3.911642972416385</v>
+        <v>3.959012702302668</v>
       </c>
       <c r="J10" t="n">
         <v>95</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6.449999809265137</v>
+        <v>6.381999969482422</v>
       </c>
       <c r="I11" t="n">
-        <v>2.810852796298856</v>
+        <v>2.840802269930179</v>
       </c>
       <c r="J11" t="n">
         <v>95</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.909999847412109</v>
+        <v>7.730000019073486</v>
       </c>
       <c r="I12" t="n">
-        <v>3.286978571624921</v>
+        <v>3.363518749786025</v>
       </c>
       <c r="J12" t="n">
         <v>95</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>26.35000038146973</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="I13" t="n">
-        <v>4.212523658180257</v>
+        <v>4.252873501059675</v>
       </c>
       <c r="J13" t="n">
         <v>77</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.8560000061988831</v>
+        <v>0.8209999799728394</v>
       </c>
       <c r="I14" t="n">
-        <v>3.504672871816521</v>
+        <v>3.654080478904819</v>
       </c>
       <c r="J14" t="n">
         <v>74</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>12.06999969482422</v>
+        <v>11.63000011444092</v>
       </c>
       <c r="I15" t="n">
-        <v>2.07125108799467</v>
+        <v>2.149613048494953</v>
       </c>
       <c r="J15" t="n">
         <v>67</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3.599999904632568</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="I16" t="n">
-        <v>4.166666777045641</v>
+        <v>4.213483213791417</v>
       </c>
       <c r="J16" t="n">
         <v>67</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.397000074386597</v>
+        <v>2.365000009536743</v>
       </c>
       <c r="I17" t="n">
-        <v>4.338756644661935</v>
+        <v>4.397462984381617</v>
       </c>
       <c r="J17" t="n">
         <v>60</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>8.067999839782715</v>
+        <v>8.031999588012695</v>
       </c>
       <c r="I18" t="n">
-        <v>3.594447270189958</v>
+        <v>3.610557954121519</v>
       </c>
       <c r="J18" t="n">
         <v>60</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>34.66999816894531</v>
+        <v>33.7599983215332</v>
       </c>
       <c r="I19" t="n">
-        <v>4.730314642672766</v>
+        <v>4.857820146732518</v>
       </c>
       <c r="J19" t="n">
         <v>60</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>33.22999954223633</v>
+        <v>32.33000183105469</v>
       </c>
       <c r="I20" t="n">
-        <v>6.018657922212547</v>
+        <v>6.186204413013344</v>
       </c>
       <c r="J20" t="n">
         <v>60</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3.769999980926514</v>
+        <v>3.624000072479248</v>
       </c>
       <c r="I21" t="n">
-        <v>2.652519907319046</v>
+        <v>2.759381843267682</v>
       </c>
       <c r="J21" t="n">
         <v>60</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>38.29999923706055</v>
+        <v>37.5</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3876240286092341</v>
+        <v>0.3958933333333334</v>
       </c>
       <c r="J22" t="n">
         <v>60</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>22.15999984741211</v>
+        <v>22.05999946594238</v>
       </c>
       <c r="I23" t="n">
-        <v>4.151624577323449</v>
+        <v>4.170444343937333</v>
       </c>
       <c r="J23" t="n">
         <v>60</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>7.949999809265137</v>
+        <v>7.554999828338623</v>
       </c>
       <c r="I24" t="n">
-        <v>3.773584996195499</v>
+        <v>3.970880302004868</v>
       </c>
       <c r="J24" t="n">
         <v>60</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>75.86000061035156</v>
+        <v>74.18000030517578</v>
       </c>
       <c r="I25" t="n">
-        <v>1.370946469328245</v>
+        <v>1.401995141172082</v>
       </c>
       <c r="J25" t="n">
         <v>60</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>51.45000076293945</v>
+        <v>51.29999923706055</v>
       </c>
       <c r="I26" t="n">
-        <v>4.275996049323108</v>
+        <v>4.288499089120179</v>
       </c>
       <c r="J26" t="n">
         <v>60</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>7.239999771118164</v>
+        <v>6.967000007629395</v>
       </c>
       <c r="I27" t="n">
-        <v>11.87845341419368</v>
+        <v>12.34390697657865</v>
       </c>
       <c r="J27" t="n">
         <v>60</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>11.16499996185303</v>
+        <v>10.72999954223633</v>
       </c>
       <c r="I28" t="n">
-        <v>5.01567399832806</v>
+        <v>5.219012338217545</v>
       </c>
       <c r="J28" t="n">
         <v>60</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.830000042915344</v>
+        <v>1.784999966621399</v>
       </c>
       <c r="I29" t="n">
-        <v>2.185792298467744</v>
+        <v>2.240896400447051</v>
       </c>
       <c r="J29" t="n">
         <v>60</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>9.020000457763672</v>
+        <v>8.779999732971191</v>
       </c>
       <c r="I30" t="n">
-        <v>3.325942181541518</v>
+        <v>3.416856595945233</v>
       </c>
       <c r="J30" t="n">
         <v>60</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.319999933242798</v>
+        <v>2.299999952316284</v>
       </c>
       <c r="I31" t="n">
-        <v>4.655172547744092</v>
+        <v>4.695652271263543</v>
       </c>
       <c r="J31" t="n">
         <v>60</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>63.59999847412109</v>
+        <v>62</v>
       </c>
       <c r="I32" t="n">
-        <v>3.238993788401137</v>
+        <v>3.32258064516129</v>
       </c>
       <c r="J32" t="n">
         <v>60</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>14.72000026702881</v>
+        <v>14.27999973297119</v>
       </c>
       <c r="I33" t="n">
-        <v>5.095108603224132</v>
+        <v>5.252100938547777</v>
       </c>
       <c r="J33" t="n">
         <v>60</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>14.92000007629395</v>
+        <v>14.42000007629395</v>
       </c>
       <c r="I34" t="n">
-        <v>2.010723850307905</v>
+        <v>2.080443817009344</v>
       </c>
       <c r="J34" t="n">
         <v>60</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>41</v>
+        <v>39.70000076293945</v>
       </c>
       <c r="I35" t="n">
-        <v>2.073170731707317</v>
+        <v>2.141057893362782</v>
       </c>
       <c r="J35" t="n">
         <v>60</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>31.42000007629395</v>
+        <v>30.04000091552734</v>
       </c>
       <c r="I36" t="n">
-        <v>2.705283252501695</v>
+        <v>2.829560499649134</v>
       </c>
       <c r="J36" t="n">
         <v>60</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.659999847412109</v>
+        <v>5.5</v>
       </c>
       <c r="I37" t="n">
-        <v>3.533568999855095</v>
+        <v>3.636363636363637</v>
       </c>
       <c r="J37" t="n">
         <v>60</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>22.1200008392334</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="I38" t="n">
-        <v>4.520795488517063</v>
+        <v>4.484305086154855</v>
       </c>
       <c r="J38" t="n">
         <v>60</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>19.14999961853027</v>
+        <v>18.40500068664551</v>
       </c>
       <c r="I40" t="n">
-        <v>4.125326452934056</v>
+        <v>4.292311711638328</v>
       </c>
       <c r="J40" t="n">
         <v>60</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4.480000019073486</v>
+        <v>4.489999771118164</v>
       </c>
       <c r="I41" t="n">
-        <v>2.075892848304796</v>
+        <v>2.071269593335409</v>
       </c>
       <c r="J41" t="n">
         <v>60</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.889999985694885</v>
+        <v>2.019999980926514</v>
       </c>
       <c r="I42" t="n">
-        <v>3.17460319863125</v>
+        <v>2.970297057749466</v>
       </c>
       <c r="J42" t="n">
         <v>60</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>5.960000038146973</v>
+        <v>5.559999942779541</v>
       </c>
       <c r="I43" t="n">
-        <v>1.728187908401823</v>
+        <v>1.852518004676606</v>
       </c>
       <c r="J43" t="n">
         <v>60</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>5.214000225067139</v>
+        <v>5.078000068664551</v>
       </c>
       <c r="I44" t="n">
-        <v>3.644035132306759</v>
+        <v>3.741630512619658</v>
       </c>
       <c r="J44" t="n">
         <v>60</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>10.15999984741211</v>
+        <v>9.904999732971191</v>
       </c>
       <c r="I45" t="n">
-        <v>4.251968567795169</v>
+        <v>4.361433736964003</v>
       </c>
       <c r="J45" t="n">
         <v>60</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>25.21999931335449</v>
+        <v>24.95999908447266</v>
       </c>
       <c r="I46" t="n">
-        <v>1.744647152972012</v>
+        <v>1.762820577480386</v>
       </c>
       <c r="J46" t="n">
         <v>60</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>6.829999923706055</v>
+        <v>6.449999809265137</v>
       </c>
       <c r="I47" t="n">
-        <v>6.881405640557772</v>
+        <v>7.286821920907129</v>
       </c>
       <c r="J47" t="n">
         <v>60</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>53.11999893188477</v>
+        <v>51.7400016784668</v>
       </c>
       <c r="I48" t="n">
-        <v>2.635542221669104</v>
+        <v>2.705836788912694</v>
       </c>
       <c r="J48" t="n">
         <v>60</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2.821000099182129</v>
+        <v>2.875</v>
       </c>
       <c r="I49" t="n">
-        <v>10.63452638966502</v>
+        <v>10.43478260869565</v>
       </c>
       <c r="J49" t="n">
         <v>60</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>80.05000305175781</v>
+        <v>81.25</v>
       </c>
       <c r="I50" t="n">
-        <v>1.686445906975335</v>
+        <v>1.661538461538461</v>
       </c>
       <c r="J50" t="n">
         <v>60</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.381999969482422</v>
+        <v>3.41100001335144</v>
       </c>
       <c r="I51" t="n">
-        <v>5.026611517859258</v>
+        <v>4.983875676768713</v>
       </c>
       <c r="J51" t="n">
         <v>60</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>4.619999885559082</v>
+        <v>4.679999828338623</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8658008872474131</v>
+        <v>0.8547008860510965</v>
       </c>
       <c r="J52" t="n">
         <v>60</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>29.14999961853027</v>
+        <v>28.54999923706055</v>
       </c>
       <c r="I53" t="n">
-        <v>3.602058366177572</v>
+        <v>3.677758417019509</v>
       </c>
       <c r="J53" t="n">
         <v>60</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>24.19000053405762</v>
+        <v>24.18000030517578</v>
       </c>
       <c r="I54" t="n">
-        <v>2.480363731928187</v>
+        <v>2.481389546846154</v>
       </c>
       <c r="J54" t="n">
         <v>60</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>30.89999961853027</v>
+        <v>30.5</v>
       </c>
       <c r="I55" t="n">
-        <v>1.132686098125743</v>
+        <v>1.147540983606557</v>
       </c>
       <c r="J55" t="n">
         <v>60</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2.441999912261963</v>
+        <v>2.319999933242798</v>
       </c>
       <c r="I56" t="n">
-        <v>10.64701102954457</v>
+        <v>11.20689687419874</v>
       </c>
       <c r="J56" t="n">
         <v>60</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>10.30000019073486</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="I57" t="n">
-        <v>3.39805818950212</v>
+        <v>3.465346403769827</v>
       </c>
       <c r="J57" t="n">
         <v>53</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>14.81999969482422</v>
+        <v>13.9399995803833</v>
       </c>
       <c r="I58" t="n">
-        <v>3.373819232767066</v>
+        <v>3.586800681856633</v>
       </c>
       <c r="J58" t="n">
         <v>53</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>6.599999904632568</v>
+        <v>6.420000076293945</v>
       </c>
       <c r="I59" t="n">
-        <v>3.333333381498703</v>
+        <v>3.426791236535292</v>
       </c>
       <c r="J59" t="n">
         <v>53</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>3.519999980926514</v>
+        <v>3.430000066757202</v>
       </c>
       <c r="I60" t="n">
-        <v>4.545454570084565</v>
+        <v>4.664722941281676</v>
       </c>
       <c r="J60" t="n">
         <v>46</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>18.70000076293945</v>
+        <v>18.76000022888184</v>
       </c>
       <c r="I61" t="n">
-        <v>3.262031952474178</v>
+        <v>3.251599107450321</v>
       </c>
       <c r="J61" t="n">
         <v>46</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>8.640000343322754</v>
+        <v>8.649999618530273</v>
       </c>
       <c r="I62" t="n">
-        <v>5.908564580029553</v>
+        <v>5.901734364315953</v>
       </c>
       <c r="J62" t="n">
         <v>46</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>7.739999771118164</v>
+        <v>7.170000076293945</v>
       </c>
       <c r="I63" t="n">
-        <v>3.488372196178945</v>
+        <v>3.76569033649939</v>
       </c>
       <c r="J63" t="n">
         <v>46</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>4.650000095367432</v>
+        <v>4.554999828338623</v>
       </c>
       <c r="I64" t="n">
-        <v>7.526881566060352</v>
+        <v>7.68386417541662</v>
       </c>
       <c r="J64" t="n">
         <v>46</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>19</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="I65" t="n">
-        <v>3.947368421052631</v>
+        <v>4.032257981818046</v>
       </c>
       <c r="J65" t="n">
         <v>46</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10.35000038146973</v>
+        <v>10.19999980926514</v>
       </c>
       <c r="I66" t="n">
-        <v>4.154589218855071</v>
+        <v>4.215686353341016</v>
       </c>
       <c r="J66" t="n">
         <v>46</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>4.125</v>
+        <v>4</v>
       </c>
       <c r="I67" t="n">
-        <v>3.636363636363636</v>
+        <v>3.75</v>
       </c>
       <c r="J67" t="n">
         <v>46</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>11.72000026702881</v>
+        <v>11.5</v>
       </c>
       <c r="I68" t="n">
-        <v>1.682329313205598</v>
+        <v>1.714513043478261</v>
       </c>
       <c r="J68" t="n">
         <v>46</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>25.75</v>
+        <v>24.79999923706055</v>
       </c>
       <c r="I69" t="n">
-        <v>4.271844660194176</v>
+        <v>4.435484007419586</v>
       </c>
       <c r="J69" t="n">
         <v>46</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>37</v>
+        <v>35.79999923706055</v>
       </c>
       <c r="I70" t="n">
-        <v>1.27027027027027</v>
+        <v>1.312849189989509</v>
       </c>
       <c r="J70" t="n">
         <v>46</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>74.80000305175781</v>
+        <v>73.30000305175781</v>
       </c>
       <c r="I71" t="n">
-        <v>1.60427800941353</v>
+        <v>1.637107708102916</v>
       </c>
       <c r="J71" t="n">
         <v>46</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>22.70000076293945</v>
+        <v>22.25</v>
       </c>
       <c r="I72" t="n">
-        <v>1.189427272799075</v>
+        <v>1.213483146067416</v>
       </c>
       <c r="J72" t="n">
         <v>46</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>10.19999980926514</v>
+        <v>10.05000019073486</v>
       </c>
       <c r="I73" t="n">
-        <v>3.725490265743223</v>
+        <v>3.78109445560333</v>
       </c>
       <c r="J73" t="n">
         <v>46</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>27.70000076293945</v>
+        <v>27.25</v>
       </c>
       <c r="I74" t="n">
-        <v>1.083032461144831</v>
+        <v>1.10091743119266</v>
       </c>
       <c r="J74" t="n">
         <v>46</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>5.920000076293945</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I75" t="n">
-        <v>2.702702667871647</v>
+        <v>2.69360266765502</v>
       </c>
       <c r="J75" t="n">
         <v>39</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>2.214999914169312</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I76" t="n">
-        <v>2.93453735976224</v>
+        <v>2.981651284840964</v>
       </c>
       <c r="J76" t="n">
         <v>39</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>7.340000152587891</v>
+        <v>7.179999828338623</v>
       </c>
       <c r="I77" t="n">
-        <v>3.405994479603064</v>
+        <v>3.481894233663894</v>
       </c>
       <c r="J77" t="n">
         <v>39</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>6.724999904632568</v>
+        <v>6.650000095367432</v>
       </c>
       <c r="I79" t="n">
-        <v>7.434944343353391</v>
+        <v>7.518796884654384</v>
       </c>
       <c r="J79" t="n">
         <v>32</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>17.06999969482422</v>
+        <v>16.71999931335449</v>
       </c>
       <c r="I80" t="n">
-        <v>3.807850097367524</v>
+        <v>3.887559968264091</v>
       </c>
       <c r="J80" t="n">
         <v>32</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>11.89999961853027</v>
+        <v>11.57999992370605</v>
       </c>
       <c r="I81" t="n">
-        <v>4.537815271515895</v>
+        <v>4.663212465956381</v>
       </c>
       <c r="J81" t="n">
         <v>32</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>6.032000064849854</v>
+        <v>5.98199987411499</v>
       </c>
       <c r="I82" t="n">
-        <v>1.657824915863776</v>
+        <v>1.671681746980888</v>
       </c>
       <c r="J82" t="n">
         <v>32</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>8.520000457763672</v>
+        <v>8.119999885559082</v>
       </c>
       <c r="I83" t="n">
-        <v>1.877934171402577</v>
+        <v>1.97044337752455</v>
       </c>
       <c r="J83" t="n">
         <v>32</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>290</v>
+        <v>274.2999877929688</v>
       </c>
       <c r="I84" t="n">
-        <v>1.246551724137931</v>
+        <v>1.317900168019134</v>
       </c>
       <c r="J84" t="n">
         <v>32</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>26.79999923706055</v>
+        <v>26.29999923706055</v>
       </c>
       <c r="I85" t="n">
-        <v>5.074627010135566</v>
+        <v>5.171102811606022</v>
       </c>
       <c r="J85" t="n">
         <v>32</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>13.10999965667725</v>
+        <v>12.52000045776367</v>
       </c>
       <c r="I86" t="n">
-        <v>4.462242679785617</v>
+        <v>4.672523790821753</v>
       </c>
       <c r="J86" t="n">
         <v>32</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>16.11000061035156</v>
+        <v>15.46000003814697</v>
       </c>
       <c r="I87" t="n">
-        <v>3.910614376980162</v>
+        <v>4.07503233147153</v>
       </c>
       <c r="J87" t="n">
         <v>32</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>100.0500030517578</v>
+        <v>94.66000366210938</v>
       </c>
       <c r="I88" t="n">
-        <v>0.899550197449182</v>
+        <v>0.9507711442866267</v>
       </c>
       <c r="J88" t="n">
         <v>32</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>63.88999938964844</v>
+        <v>62.0099983215332</v>
       </c>
       <c r="I89" t="n">
-        <v>2.693379271308628</v>
+        <v>2.775036359584041</v>
       </c>
       <c r="J89" t="n">
         <v>32</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1.919999957084656</v>
+        <v>1.889999985694885</v>
       </c>
       <c r="I92" t="n">
-        <v>1.770833372914544</v>
+        <v>1.798941812557709</v>
       </c>
       <c r="J92" t="n">
         <v>11</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>23.06999969482422</v>
+        <v>23.93499946594238</v>
       </c>
       <c r="I93" t="n">
-        <v>1.1270047830054</v>
+        <v>1.086275353253964</v>
       </c>
       <c r="J93" t="n">
         <v>4</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>29.11499977111816</v>
+        <v>27.79999923706055</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3091190132492436</v>
+        <v>0.3237410160789494</v>
       </c>
       <c r="J94" t="n">
         <v>4</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>51.45000076293945</v>
+        <v>51.29999923706055</v>
       </c>
       <c r="I95" t="n">
-        <v>1.263362469118191</v>
+        <v>1.267056549058235</v>
       </c>
       <c r="J95" t="n">
         <v>-24</v>
@@ -4917,7 +4917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C304"/>
+  <dimension ref="A1:C314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4967,14 +4967,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4984,14 +4984,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5008,7 +5008,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5018,14 +5018,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5035,14 +5035,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5076,7 +5076,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5229,7 +5229,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5273,14 +5273,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5297,7 +5297,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5331,7 +5331,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5365,7 +5365,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5382,7 +5382,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5399,7 +5399,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5416,7 +5416,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5450,7 +5450,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5477,14 +5477,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5494,14 +5494,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5518,7 +5518,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5535,7 +5535,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5552,7 +5552,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5569,7 +5569,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5579,14 +5579,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5620,7 +5620,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5630,14 +5630,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5654,7 +5654,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5671,7 +5671,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5688,7 +5688,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5705,7 +5705,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5722,7 +5722,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5732,14 +5732,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5749,14 +5749,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5773,7 +5773,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5790,12 +5790,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5807,41 +5807,41 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5851,14 +5851,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5875,7 +5875,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5892,7 +5892,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5909,7 +5909,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5926,7 +5926,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5943,7 +5943,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5960,7 +5960,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5970,19 +5970,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5994,46 +5994,46 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6045,12 +6045,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6062,29 +6062,29 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6096,29 +6096,29 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6130,12 +6130,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6147,7 +6147,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6164,7 +6164,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6181,7 +6181,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6198,7 +6198,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6208,14 +6208,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6232,7 +6232,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6242,14 +6242,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6259,14 +6259,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6276,14 +6276,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6300,7 +6300,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6310,14 +6310,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6334,7 +6334,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6351,7 +6351,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6368,12 +6368,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6385,12 +6385,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6402,12 +6402,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6419,29 +6419,29 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6453,29 +6453,29 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6487,12 +6487,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6504,29 +6504,29 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6555,7 +6555,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6565,14 +6565,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6582,14 +6582,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6606,7 +6606,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6623,7 +6623,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6640,7 +6640,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6657,7 +6657,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6674,7 +6674,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6684,14 +6684,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6708,7 +6708,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6725,7 +6725,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6742,7 +6742,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6759,7 +6759,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6769,14 +6769,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6793,7 +6793,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6810,7 +6810,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6827,29 +6827,29 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6861,29 +6861,29 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6895,29 +6895,29 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6929,12 +6929,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6946,12 +6946,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6963,12 +6963,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6980,12 +6980,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6997,7 +6997,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7014,7 +7014,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7048,7 +7048,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7065,7 +7065,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7082,7 +7082,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7099,7 +7099,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7109,14 +7109,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7133,7 +7133,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7167,7 +7167,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7184,7 +7184,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7201,7 +7201,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7218,7 +7218,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7235,7 +7235,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7252,7 +7252,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7269,7 +7269,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7286,7 +7286,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7303,7 +7303,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7320,7 +7320,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7337,7 +7337,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7354,7 +7354,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7371,7 +7371,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7388,7 +7388,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7405,7 +7405,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7422,12 +7422,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7439,12 +7439,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7456,29 +7456,29 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7490,12 +7490,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7507,12 +7507,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7524,12 +7524,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7541,12 +7541,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7558,12 +7558,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7575,12 +7575,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7592,7 +7592,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7609,7 +7609,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7626,7 +7626,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7643,7 +7643,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7660,7 +7660,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7677,7 +7677,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7694,7 +7694,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7711,7 +7711,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7745,7 +7745,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7762,7 +7762,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7779,7 +7779,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7796,7 +7796,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7813,7 +7813,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7830,7 +7830,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7847,7 +7847,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7864,7 +7864,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7881,7 +7881,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7898,7 +7898,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -7915,7 +7915,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -7932,7 +7932,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -7942,14 +7942,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -7966,7 +7966,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -7976,14 +7976,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8000,7 +8000,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8017,7 +8017,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8027,14 +8027,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8051,7 +8051,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8068,7 +8068,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8085,7 +8085,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8102,7 +8102,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8119,7 +8119,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8136,7 +8136,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8153,7 +8153,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8170,7 +8170,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8187,7 +8187,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8204,7 +8204,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8214,14 +8214,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8231,14 +8231,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8255,7 +8255,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8272,7 +8272,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8289,12 +8289,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8306,12 +8306,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8323,12 +8323,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -8340,46 +8340,46 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -8391,12 +8391,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -8408,29 +8408,29 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -8442,12 +8442,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -8476,7 +8476,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -8493,7 +8493,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -8510,7 +8510,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -8527,7 +8527,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -8544,7 +8544,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -8561,7 +8561,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -8578,7 +8578,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -8588,14 +8588,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -8612,7 +8612,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -8622,14 +8622,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -8639,14 +8639,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -8663,7 +8663,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -8680,7 +8680,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -8697,7 +8697,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -8714,7 +8714,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -8731,7 +8731,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -8748,7 +8748,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -8758,14 +8758,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -8782,7 +8782,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -8792,14 +8792,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -8816,7 +8816,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -8833,7 +8833,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -8843,14 +8843,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -8867,7 +8867,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -8877,14 +8877,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -8894,14 +8894,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -8918,63 +8918,63 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8986,12 +8986,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -9003,29 +9003,29 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9037,29 +9037,29 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9071,46 +9071,46 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9122,29 +9122,29 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9156,80 +9156,80 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9241,63 +9241,63 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9309,63 +9309,63 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9377,97 +9377,97 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9479,12 +9479,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9496,41 +9496,41 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -9540,14 +9540,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -9557,14 +9557,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -9574,14 +9574,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -9591,14 +9591,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -9615,7 +9615,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -9625,14 +9625,14 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -9642,14 +9642,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -9666,7 +9666,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -9676,19 +9676,19 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9700,160 +9700,160 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -9863,14 +9863,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -9880,14 +9880,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9904,7 +9904,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -9921,7 +9921,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -9938,7 +9938,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9948,14 +9948,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -9972,7 +9972,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -9982,14 +9982,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -9999,14 +9999,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -10023,29 +10023,29 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -10057,12 +10057,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -10074,15 +10074,185 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>IGD SIIQ S.p.A.</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>INTERCOS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>MAIRE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>BANCA IFIS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
           <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>FIDIA S.p.A</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>BEEWIZE</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr">
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>IGD SIIQ S.p.A.</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Banca Generali S.p.A.</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -10099,188 +10269,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BREMBO N.V.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NL0015001KT6</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7.949999809265137</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3.773584996195499</v>
-      </c>
-      <c r="I2" t="n">
-        <v>60</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005186371</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5.960000038146973</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.103</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1.728187908401823</v>
-      </c>
-      <c r="I3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Pharmanutra S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0005274094</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>74.80000305175781</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1.60427800941353</v>
-      </c>
-      <c r="I4" t="n">
-        <v>46</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10291,44 +10282,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>